--- a/src/attributions/attributions_ig_traj_479.xlsx
+++ b/src/attributions/attributions_ig_traj_479.xlsx
@@ -2140,52 +2140,52 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.07139953444969278</v>
+        <v>0.1122984161863071</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01602168511262622</v>
+        <v>-0.0224638345379172</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.05505460815880316</v>
+        <v>-0.08527441731382929</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03875142239040252</v>
+        <v>0.138134809261738</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01289194415297034</v>
+        <v>-0.02761283556691631</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.05783524818425716</v>
+        <v>-0.06986510525233927</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -2194,49 +2194,49 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0009713226172184085</v>
+        <v>0.004660064927809556</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004996205439942352</v>
+        <v>0.02744102244369793</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.003494337967196825</v>
+        <v>0.01261433510200153</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.009582214647650683</v>
+        <v>-0.05409776606246029</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0265208422713107</v>
+        <v>-0.07615476891480069</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.0002001635550124991</v>
+        <v>-0.06490411695863546</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0135709014575706</v>
+        <v>0.01479700399859013</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01162795383168634</v>
+        <v>-0.03367779300918115</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.02004141429854002</v>
+        <v>-0.03775263538848452</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.08400873207677031</v>
+        <v>0.3188885422422665</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,79 +2284,79 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01396814899144188</v>
+        <v>-0.05549306737415514</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.07014904026721261</v>
+        <v>-0.05126183668860743</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01378412238283536</v>
+        <v>-0.003849099242585636</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01248622332760605</v>
+        <v>-0.02574002206761057</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.003706436192815624</v>
+        <v>-0.007966112902138573</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02832267135097588</v>
+        <v>0.04306651200395734</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.004344373891084968</v>
+        <v>0.07979140375947988</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01299916743226717</v>
+        <v>0.07321453862676035</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04330448078485438</v>
+        <v>0.1283112482917965</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,148 +2365,148 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01547950984393487</v>
+        <v>-0.07062783421826625</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.01177691197368583</v>
+        <v>-0.1013551996160853</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.0191982293618027</v>
+        <v>-0.04679009741214576</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.0009107059939252003</v>
+        <v>0.001437481418186543</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03525969039246946</v>
+        <v>0.06850914033146351</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0044135791433414</v>
+        <v>-0.1215257456688819</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.004892777546285318</v>
+        <v>0.07943357471734537</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.006933069834596335</v>
+        <v>0.05136807553656646</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01440198234858509</v>
+        <v>-0.05127448348123535</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.005032926707794378</v>
+        <v>-0.008518178662472425</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03745003030387135</v>
+        <v>0.0634348023001559</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01446196455978014</v>
+        <v>-0.01123428564280729</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.02222363720395278</v>
+        <v>-0.05773253109923399</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.05574692607718632</v>
+        <v>0.003514369418695329</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01238430664999086</v>
+        <v>-0.02488690876170149</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01752200441872206</v>
+        <v>0.04698696385295107</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01158600315035775</v>
+        <v>0.08739935848220644</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001632261936842522</v>
+        <v>-0.005886562048823024</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.001816831419795695</v>
+        <v>0.002377514546035885</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.03211790109698794</v>
+        <v>-0.06167105710976983</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2542,64 +2542,64 @@
         <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.006323196793432335</v>
+        <v>-0.0482734201082168</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.003222585762781166</v>
+        <v>-0.04201135187313023</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01353617041175211</v>
+        <v>0.0341735202639471</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.004006907481916758</v>
+        <v>0.01596279807651449</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01184983990891016</v>
+        <v>-0.0510553132200523</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.03761840477105722</v>
+        <v>0.05157872438701574</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01542712500777567</v>
+        <v>-0.05669470845336232</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,37 +2608,37 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.002185644301545232</v>
+        <v>-0.01750810773340867</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03437566424741156</v>
+        <v>0.05475021825266449</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01704494540380833</v>
+        <v>-0.08932221631204017</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01202364653694092</v>
+        <v>0.01903475931852579</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.005470727618429547</v>
+        <v>-0.02794210190094338</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0002181651313858191</v>
+        <v>0.04075479644633832</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.007602346609671556</v>
+        <v>0.002422647467009429</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03323096186890812</v>
+        <v>0.04817944324826266</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02002630451299361</v>
+        <v>-0.007094388309009443</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,63 +2689,63 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.01056423402104876</v>
+        <v>0.04395789317091733</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1634903240369725</v>
+        <v>0.2127816782718666</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.05957912297632333</v>
+        <v>-0.09179484307311371</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0732589339777909</v>
+        <v>-0.02891306852953883</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09262755216098355</v>
+        <v>0.1699188813928079</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01937481357308456</v>
+        <v>-0.04175741976446953</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.07568070824455399</v>
+        <v>-0.0451723259886197</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,19 +2760,19 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.513858273526294e-11</v>
+        <v>3.616098232579308e-11</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.830542725352905e-13</v>
+        <v>1.681222182993701e-12</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.004197563479946471</v>
+        <v>-0.002239269318121729</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
@@ -2790,43 +2790,43 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.06786601717092809</v>
+        <v>-0.006473710351439781</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01473980033001599</v>
+        <v>-0.09689019525738603</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02094982317661078</v>
+        <v>-0.07264357012109735</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0008438262524730879</v>
+        <v>0.09698448757150974</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.0450028082943638</v>
+        <v>-0.02677893726600157</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08907633778704487</v>
+        <v>0.06386357864441272</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,31 +2835,31 @@
         <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3566902099485909</v>
+        <v>0.3130596559502296</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.00393691882567593</v>
+        <v>-0.1467514663895314</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1220902068868685</v>
+        <v>-0.171031949775993</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2868,19 +2868,19 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.00346457400136604</v>
+        <v>-0.006608947691555357</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02599717737560096</v>
+        <v>0.001752126214559023</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.04782503523758914</v>
+        <v>-0.003792138564081381</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1075411697164742</v>
+        <v>-0.008393252487308094</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.04421294603511897</v>
+        <v>0.06138380200916446</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1243073865917837</v>
+        <v>0.08726591063397987</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,46 +2925,46 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1721714011798843</v>
+        <v>0.2218693980600882</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.001753157842138467</v>
+        <v>-0.1029602639627321</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0233428236736041</v>
+        <v>-0.008735886538383997</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05057129329459337</v>
+        <v>-0.1075086046519783</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01760392661967825</v>
+        <v>0.09240198082207754</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001185305708692831</v>
+        <v>0.01515440939792489</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
@@ -2979,22 +2979,22 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.03204079836975427</v>
+        <v>-0.122464605610682</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.05018879137812214</v>
+        <v>0.048924138256741</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.124317553066056</v>
+        <v>0.06476127879344595</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>-0</v>
@@ -3006,19 +3006,19 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03065438188930058</v>
+        <v>-0.1189153471897002</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03453509671886671</v>
+        <v>0.1000184271666996</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01939790494718896</v>
+        <v>0.01926158563589968</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3033,22 +3033,22 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001261243071633256</v>
+        <v>-0.006727680837573372</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.01719840338708038</v>
+        <v>0.02818900726473219</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.02127190549544266</v>
+        <v>-0.07241519925248899</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
@@ -3060,52 +3060,52 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06924418230896126</v>
+        <v>-0.0729415722091369</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.01798753109520717</v>
+        <v>0.01809880792466001</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.002361295953502642</v>
+        <v>-0.04300393509212192</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.02043022053265629</v>
+        <v>0.03580054807263208</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04028269989057206</v>
+        <v>0.04087191076363626</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02271948278100969</v>
+        <v>-3.740409695765832e-05</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,19 +3114,19 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03674927854501311</v>
+        <v>-0.06705126236899001</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.05157250126463357</v>
+        <v>0.107380869072134</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.07452795349604825</v>
+        <v>0.03449570372411497</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03528377349384002</v>
+        <v>-0.0501566885775926</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.04574729390974702</v>
+        <v>0.05663213773733304</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.003066221585305524</v>
+        <v>-0.04092690289593535</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0395698749599576</v>
+        <v>-0.1280806468567853</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03232818647214987</v>
+        <v>0.1092717790315349</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01916878473027629</v>
+        <v>0.01023663288196545</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,49 +3192,49 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.06369890601507212</v>
+        <v>-0.0818987558912464</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.0434416281583985</v>
+        <v>-0.05034086786562695</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.01050397851638606</v>
+        <v>0.075116630846779</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.05381818408062922</v>
+        <v>0.03612697437375714</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.04097617148961146</v>
+        <v>0.1204323301680283</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.05888860022554488</v>
+        <v>-0.08212496024989166</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.03739993075518917</v>
+        <v>-0.1050088447709859</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.006072468082656691</v>
+        <v>0.05594517976720087</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02398664292917492</v>
+        <v>0.03117596876832582</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01162107307099911</v>
+        <v>0.01834550600939702</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.006712145030263491</v>
+        <v>-0.0121506313896318</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007352693486814473</v>
+        <v>0.04644705773574612</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01588813511307793</v>
+        <v>0.01098811709057413</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.008740035643631339</v>
+        <v>-0.01190240783038568</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000272544135146705</v>
+        <v>-8.305117960235334e-06</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.842671809587223e-12</v>
+        <v>-1.208855152918571e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003882931987151454</v>
+        <v>-0.0002385894158142962</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01834431475142168</v>
+        <v>-0.01402633208052313</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02268481542407502</v>
+        <v>-0.05503948073597108</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001521891114349768</v>
+        <v>-0.01424675066657508</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.004313642545274915</v>
+        <v>0.01057201924926384</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,52 +3395,52 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.02002333504984137</v>
+        <v>-0.01308252702763463</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.00518995609702015</v>
+        <v>-0.02273024252131909</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0480941835441079</v>
+        <v>0.08848412957421285</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.008982609948899841</v>
+        <v>-0.01695821946784778</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01045515388742351</v>
+        <v>-0.01804898443952835</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.003613558147995633</v>
+        <v>-0.00372881142716492</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.009666053031829588</v>
+        <v>-0.005783210069082081</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.002301195661922072</v>
+        <v>0.004101968128895774</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02994688841905552</v>
+        <v>0.01738513888323781</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01385458636910079</v>
+        <v>0.03867908284924831</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01100811466509395</v>
+        <v>0.03088773639362677</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01558185984681623</v>
+        <v>0.0383729050531289</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01081294401010686</v>
+        <v>0.002203824280436291</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01705657079917652</v>
+        <v>-0.03296026006793875</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,76 +3521,76 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.000994583342171552</v>
+        <v>-0.00958275455319439</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.000257266740198107</v>
+        <v>-0.002261335696004249</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.005845035532951343</v>
+        <v>0.02180342809871777</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001121286592430041</v>
+        <v>-0.03228917423696114</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0002498544898934007</v>
+        <v>0.03989977010577326</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01297910544349893</v>
+        <v>0.02466140437376495</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.003241507185262722</v>
+        <v>-0.01210628500485457</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0009134729061021752</v>
+        <v>-0.004053158374746351</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.00534450624004482</v>
+        <v>0.01921855773623784</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3599,22 +3599,22 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0002725561908093833</v>
+        <v>-0.0163845276594214</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0001769591339785926</v>
+        <v>-0.0009627358576013127</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01854352739842934</v>
+        <v>-0.001754562359574286</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,25 +3623,25 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.002952960622473533</v>
+        <v>-0.01383412198033855</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01532805418772906</v>
+        <v>-0.0008178220270340482</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001295479441033427</v>
+        <v>0.02822697646674206</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3653,10 +3653,10 @@
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01261083050120959</v>
+        <v>-0.01164701453282692</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,16 +3665,16 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.008392274698628872</v>
+        <v>0.002829224638052409</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.0001416575401298109</v>
+        <v>0.02141741481586771</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
@@ -3683,76 +3683,76 @@
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.004990822122341513</v>
+        <v>-0.009105563944476092</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001088902198944256</v>
+        <v>-0.02021266392604018</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.003112247882666975</v>
+        <v>0.002775766240540698</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.0005190996276297727</v>
+        <v>0.0001745521632992073</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01495114580838899</v>
+        <v>-0.002374222812706214</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03267055687016056</v>
+        <v>0.01297427298624845</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004201732321611864</v>
+        <v>-0.01563449545796243</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0006050135360783761</v>
+        <v>-0.009103354011172316</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.008679327691727469</v>
+        <v>0.01406584798533352</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,22 +3761,22 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.008880892367668019</v>
+        <v>-0.01758504453084281</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01443469331389967</v>
+        <v>0.01567553779746087</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02187545948153116</v>
+        <v>0.003088203662142428</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.009087733667304544</v>
+        <v>0.01166038431637823</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.001313067307588127</v>
+        <v>-0.000811146752960225</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.002802555368670244</v>
+        <v>-0.0342020146469916</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,31 +3812,31 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02002770484562873</v>
+        <v>0.009556063260979589</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.00499531319460852</v>
+        <v>0.01553778026792428</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1066362792539601</v>
+        <v>0.05244978388898346</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01760568760079733</v>
+        <v>-0.02431208720745472</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01575065426123854</v>
+        <v>-0.005152260539926866</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04644229878619352</v>
+        <v>0.06902652654026446</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0634254616860689</v>
+        <v>-0.02484588397222215</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.02020734686837751</v>
+        <v>-0.004562200274173372</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003899286224012389</v>
+        <v>-0.001305253036536143</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.001238751616171664</v>
+        <v>-0.002672338284165479</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00102904111243655</v>
+        <v>0.0009814920850152633</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04091042878291111</v>
+        <v>-0.0136885409475952</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02887825283920527</v>
+        <v>-0.01828147982545933</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01528449742508059</v>
+        <v>-0.0002084291940358222</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03055414462940071</v>
+        <v>0.02478996774256766</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02782205812592124</v>
+        <v>-0.006558622349050302</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01725468776031048</v>
+        <v>-0.004718409944162815</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.192095638171095</v>
+        <v>0.09253534255451579</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.07386015125062045</v>
+        <v>-0.01665208851070851</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.001012346858955811</v>
+        <v>0.009182391523893588</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.009251301741454381</v>
+        <v>-0.002815756551314225</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,79 +4018,79 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.03599779679418483</v>
+        <v>-0.01167486093298342</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01348032067064879</v>
+        <v>0.007429868284981873</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02282276823259587</v>
+        <v>0.01289647865461573</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08368079410336023</v>
+        <v>0.03629341846224159</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02925828950284317</v>
+        <v>0.01176001785655461</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09755763751352983</v>
+        <v>0.05048051594322516</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01063939724810602</v>
+        <v>-0.02093973678816179</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.006667870680620413</v>
+        <v>-0.01714894940049552</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02319411246316869</v>
+        <v>-0.02236685156283414</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,37 +4099,37 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.001520004607055848</v>
+        <v>0.008525422355738983</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0286836853406205</v>
+        <v>0.0112672002233748</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02508740823623158</v>
+        <v>-0.04195184706253693</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.01898944259323247</v>
+        <v>0.006593014345531023</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.01107860265088655</v>
+        <v>0.01697514047163365</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01862374168460578</v>
+        <v>-0.02317781687921457</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,34 +4153,34 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.007087569618733087</v>
+        <v>0.004694235135901268</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02790261079175445</v>
+        <v>0.01043430097828257</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.0763494744338898</v>
+        <v>-0.01741380021898958</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02941518104180406</v>
+        <v>-0.01094030784847516</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,97 +4189,97 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.008329877716224449</v>
+        <v>-0.006830775924355693</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0006566478780515833</v>
+        <v>-0.01804999503990715</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.003959416496685061</v>
+        <v>0.009286646613679216</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>5.862293303482847e-05</v>
+        <v>-0.02635176708066941</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.002020673567830446</v>
+        <v>0.008565280579552996</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.0167308814593141</v>
+        <v>0.007094761227853386</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.009566075120558456</v>
+        <v>-0.007427913592934282</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.001894208974476019</v>
+        <v>-0.01798740859911071</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03115187311191161</v>
+        <v>0.0005442383842853578</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03100306879417376</v>
+        <v>0.004331704814094436</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03710556108572143</v>
+        <v>-0.003930350370682021</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.003244220600435627</v>
+        <v>0.005144690607619073</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01081807293032947</v>
+        <v>0.006707994850195422</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02999792731908826</v>
+        <v>-0.02676197940749757</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.008157265661142081</v>
+        <v>0.001887305616400768</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,40 +4327,40 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0157230681779129</v>
+        <v>0.01121135208495228</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03117483206164035</v>
+        <v>-0.01615904207786936</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02404298432339338</v>
+        <v>0.007316765660668311</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01313690578621195</v>
+        <v>0.03783704398767746</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05202660894160914</v>
+        <v>0.00718953297155459</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0140120820317036</v>
+        <v>-0.01812131662315868</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
@@ -4378,19 +4378,19 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.000569356133007277</v>
+        <v>0.001854981190019156</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03820032248574179</v>
+        <v>-0.01182516457810003</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03686539638822037</v>
+        <v>0.001658186120502395</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2646396962534087</v>
+        <v>0.1918590220936608</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1280324789870224</v>
+        <v>-0.08959882856305675</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.004339887851484578</v>
+        <v>-0.04637823749020129</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,43 +5012,43 @@
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.149704965845243</v>
+        <v>0.1761073143263844</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1292716306074831</v>
+        <v>-0.127029320666441</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06554426950293017</v>
+        <v>-0.1080042731355592</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03041106612847649</v>
+        <v>0.0279045663854952</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004595290996369008</v>
+        <v>-0.005416975239871595</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002884612875003466</v>
+        <v>-0.01452650817129996</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -5057,52 +5057,52 @@
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1359008507890006</v>
+        <v>-0.01304589008160615</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.05297381042865106</v>
+        <v>-0.0838128867717516</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03551414239971426</v>
+        <v>-0.1246538093280364</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.01626764692524446</v>
+        <v>0.1659152081887905</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0339147527630265</v>
+        <v>-0.07646218434474843</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1146686920376815</v>
+        <v>0.06724958192556299</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,28 +5111,28 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4349964592814943</v>
+        <v>0.2458000961642409</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.04133216754319709</v>
+        <v>-0.0402665658887443</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.2318032231223388</v>
+        <v>-0.2936733562243169</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5147,25 +5147,25 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0004597689425939974</v>
+        <v>-0.03144938071778632</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.04806587747005046</v>
+        <v>-0.004941091163492495</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1012783034181516</v>
+        <v>0.004349363921974867</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1872410136541257</v>
+        <v>0.01753479054437189</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0114044464417693</v>
+        <v>0.01371072522271424</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1660800172853929</v>
+        <v>0.01534381774355005</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
@@ -5201,52 +5201,52 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2262707282533908</v>
+        <v>0.2265629994331748</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02231906536658064</v>
+        <v>-0.1712227894012933</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.06174711532257299</v>
+        <v>-0.07471184699688015</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06221023540227029</v>
+        <v>-0.07485052286624136</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0005381980287045412</v>
+        <v>0.08971943824228583</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02079003312506499</v>
+        <v>0.02601689653132526</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.1039561606513747</v>
+        <v>-0.08207430614192222</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1443377208097509</v>
+        <v>0.2547587050857495</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1038722649000222</v>
+        <v>0.1406671316346887</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,25 +5282,25 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03405760209331947</v>
+        <v>-0.05663989162589126</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02312989983211365</v>
+        <v>0.101865760942485</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.005251631792309681</v>
+        <v>0.04405746487005157</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01715001091604108</v>
+        <v>-0.007494619455110024</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01281743374746705</v>
+        <v>0.01811138929949409</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03475273408438201</v>
+        <v>-0.03978689912395414</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,52 +5336,52 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.06723074939463523</v>
+        <v>-0.08197227236947784</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05506438515440654</v>
+        <v>0.07390188303344958</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.00333996564853983</v>
+        <v>0.02020217085124439</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03377705131402971</v>
+        <v>0.01937889697282478</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.03892062776364633</v>
+        <v>0.0423806013826291</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.01618611569059419</v>
+        <v>-0.03756768617684109</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,22 +5390,22 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.002264410229994606</v>
+        <v>0.007226086410525224</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0589959773530827</v>
+        <v>0.06056295088784948</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04366660305393553</v>
+        <v>0.03825024228754623</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,25 +5414,25 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07697956893657786</v>
+        <v>-0.07475142762891657</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.05512944227651852</v>
+        <v>-0.07908092365029754</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01209864021094875</v>
+        <v>0.002060775368483765</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,106 +5444,106 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.04781968268576887</v>
+        <v>-0.07466035492435107</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.008834614856959787</v>
+        <v>0.1153793030215494</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0136740049834206</v>
+        <v>0.02486906350910654</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.06794325709337695</v>
+        <v>-0.01954964629732147</v>
       </c>
       <c r="FI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03365800055236019</v>
+        <v>0.01587458624268008</v>
       </c>
       <c r="FK9" t="n">
-        <v>-2.38740408106739e-05</v>
+        <v>-0.03875209291496388</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.0666647952735335</v>
+        <v>0.01179846241040217</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.06494069711644651</v>
+        <v>0.1094137642954497</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.1070223248439012</v>
+        <v>-0.1296851361095327</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.03882476972535277</v>
+        <v>-0.008572283863327401</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.08432708338912304</v>
+        <v>0.03667367657058946</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3908219075285943</v>
+        <v>0.2040894382152774</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1512159213289025</v>
+        <v>-0.2061524946761075</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1318728358704841</v>
+        <v>-0.07469450638053417</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004609632705529615</v>
+        <v>0.01489257743263818</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2280168244470099</v>
+        <v>0.178454778827816</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1342428849076075</v>
+        <v>-0.2382977068479022</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2215993028917125</v>
+        <v>-0.1378258375997263</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,115 +5599,115 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0006306156175901829</v>
+        <v>-7.918577679792447e-05</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08598627799117993</v>
+        <v>0.06408103320789568</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.02028264467151022</v>
+        <v>-0.02992065755221591</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001637758862690403</v>
+        <v>-0.06561397375923658</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0014053125379973</v>
+        <v>-0.002976855604583181</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.09325102501483253</v>
+        <v>-0.1300606354297649</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08843510927094184</v>
+        <v>-0.06098033407086537</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.04073906360424784</v>
+        <v>-0.1174192903999464</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01275472679790028</v>
+        <v>0.04119534774463295</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01611616615611691</v>
+        <v>0.122534581083089</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.06836727396240037</v>
+        <v>-0.04003269189549648</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1026806221936826</v>
+        <v>0.06426722171229547</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01558556531238518</v>
+        <v>0.01665441759162991</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6188180547958182</v>
+        <v>0.2448621081269518</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.00771316881147477</v>
+        <v>-0.07357332925970793</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2206386572729572</v>
+        <v>-0.3539547563952112</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.06621105680041539</v>
+        <v>-0.07269166649996789</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.003382698074440439</v>
+        <v>-0.03420256075594436</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.05148807455454593</v>
+        <v>-0.07682728327638165</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2337526568053145</v>
+        <v>-0.02072638055236511</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0006155225369341722</v>
+        <v>-0.04291526577146394</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2334224162478439</v>
+        <v>0.03757269428403011</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1380702653704958</v>
+        <v>0.1103495509634916</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1725467337086382</v>
+        <v>-0.02777761557182156</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.04514351897683621</v>
+        <v>0.04108798672893532</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,25 +5770,25 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.3048666777268512</v>
+        <v>0.231883804177391</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.04284765283749589</v>
+        <v>-0.1849219262267371</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.05359464003683596</v>
+        <v>-0.1911282802810761</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.009561330278816272</v>
+        <v>-0.1031429331882203</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
@@ -5797,16 +5797,16 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.0956538137723776</v>
+        <v>-0.05808301155499597</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.02072150549874699</v>
+        <v>0.1451258688283374</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.003073225236550374</v>
+        <v>0.03903754582917316</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,7 +5815,7 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.005215147099142192</v>
+        <v>-0.02447223688779046</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,43 +5824,43 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.1358404709237368</v>
+        <v>-0.01091593926331852</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.1585998832869732</v>
+        <v>0.225874123859081</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05529520791791158</v>
+        <v>0.3108458123449329</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.06487698449674976</v>
+        <v>0.05259607072885836</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.06191935176581022</v>
+        <v>-0.05165328681177238</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.05242613948345431</v>
+        <v>0.1652843301991085</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.00385975447211645</v>
+        <v>0.05235018346890855</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,25 +5869,25 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.005552999935752389</v>
+        <v>-0.01042236164449978</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.06960155576657928</v>
+        <v>-0.05631942493996691</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.033320609706617</v>
+        <v>0.06541231711422618</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.003097780588542462</v>
+        <v>-0.003357804157140388</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
@@ -5896,25 +5896,25 @@
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.001351571441211141</v>
+        <v>-0.04880810084434136</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1055040144408874</v>
+        <v>-0.03290520122097296</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.03637992336612913</v>
+        <v>0.1308130070397875</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03588819715959097</v>
+        <v>-0.05476002466839359</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,25 +5923,25 @@
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.0305490448291198</v>
+        <v>0.08827012959557798</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.02678188477734071</v>
+        <v>0.05506841230024716</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.04796098497854182</v>
+        <v>0.03505761014469217</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.0677608616665781</v>
+        <v>-0.09495219629277293</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
@@ -5950,133 +5950,133 @@
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.02665284800402118</v>
+        <v>0.1319592066165168</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.04435821644211534</v>
+        <v>0.03025052953329344</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07309068040472588</v>
+        <v>0.08223173132367742</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04023747755798153</v>
+        <v>0.04444624744488634</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.04204885535517429</v>
+        <v>-0.03286910850345837</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1070358458149199</v>
+        <v>-0.03683850989744893</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.09866403191893912</v>
+        <v>0.1528343998817444</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.04042144200430482</v>
+        <v>-0.07002465856172761</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.005376119041658617</v>
+        <v>0.03049790541925563</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.07158830351050555</v>
+        <v>-0.0684916755035664</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03885303465336321</v>
+        <v>0.1956457552511388</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02508021300245191</v>
+        <v>0.04968042089297558</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.004390096587841292</v>
+        <v>-0.0109455225620472</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.07364770362041044</v>
+        <v>-0.02809502785216438</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.04755846977946231</v>
+        <v>-0.07676779357691989</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02831752558118759</v>
+        <v>0.07735826769834735</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.004399309781326429</v>
+        <v>-0.0314525683350254</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1212914775703828</v>
+        <v>0.04178409950702225</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.08487325388990702</v>
+        <v>0.09925143390461265</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.08712865457857528</v>
+        <v>-0.2069228855917907</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6085,34 +6085,34 @@
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.01012281835384593</v>
+        <v>-0.07063143208176001</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1204343867891371</v>
+        <v>-0.02023555774382853</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03526994853906716</v>
+        <v>0.06908015075971065</v>
       </c>
       <c r="GC10" t="n">
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.02809727829323812</v>
+        <v>-0.05088070603814376</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6120,28 +6120,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1825123902271597</v>
+        <v>0.3305190376251806</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.121276828800906</v>
+        <v>-0.02748292229802804</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07179094206312067</v>
+        <v>-0.1803317758647207</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,19 +6150,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1094734691554305</v>
+        <v>0.4154693348760192</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1246381316599394</v>
+        <v>-0.09428090471687907</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.07598665250246359</v>
+        <v>-0.1427375369821843</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0280488982409446</v>
+        <v>0.06288743667576781</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.008855450740669383</v>
+        <v>-0.06546255669810161</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0259209127098245</v>
+        <v>0.01674531231737755</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04586984028912585</v>
+        <v>-0.01734503201393246</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03430388206854839</v>
+        <v>-0.2442128149364916</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02414779108190174</v>
+        <v>0.02179644374702555</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03603364916495302</v>
+        <v>0.08647987992318841</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,13 +6240,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02957608195659469</v>
+        <v>-0.06738370367973442</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.01625932541386517</v>
+        <v>-0.03225547195612505</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2096697132512972</v>
+        <v>0.5740018329020086</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,79 +6267,79 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.02805721770911297</v>
+        <v>-0.2171847830263622</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.01368420523358471</v>
+        <v>-0.04474232726793853</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03928830335454229</v>
+        <v>-0.05474163191901063</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.08102458235190854</v>
+        <v>-0.03545991706141351</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.04743799894574029</v>
+        <v>-0.08153909518748821</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1046002967425138</v>
+        <v>0.1568401872432881</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.07053501678111786</v>
+        <v>0.1552231050284942</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.03235552097058832</v>
+        <v>0.08163692071110293</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.09732572324016008</v>
+        <v>0.3680680292148781</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,43 +6348,43 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01712854135455788</v>
+        <v>-0.08490069107619623</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.02286360159943702</v>
+        <v>-0.034622486802929</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03810716477573545</v>
+        <v>-0.1235464091714601</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01463598349790979</v>
+        <v>0.01208593447700179</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01983331991805538</v>
+        <v>0.07062391334464913</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
@@ -6393,22 +6393,22 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.04380339439661761</v>
+        <v>-0.2635812666563905</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.04170394587237645</v>
+        <v>0.08437317240033752</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.01697782053190654</v>
+        <v>0.005716071068952356</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,28 +6417,28 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02082622887820391</v>
+        <v>-0.1059871802739296</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01342196494419003</v>
+        <v>-0.01260162259730346</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02275537303411986</v>
+        <v>0.07225115160330713</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.0514849480939679</v>
+        <v>-0.08260046066588499</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,37 +6456,37 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01599005349853938</v>
+        <v>-0.1414184418264681</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.004303663811978555</v>
+        <v>-0.00991272442667236</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.04299513276828729</v>
+        <v>-0.07338135832205629</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01598156824759238</v>
+        <v>-0.03172902400729759</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.03711687997428893</v>
+        <v>-0.0197965778049962</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6498,10 +6498,10 @@
         <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>3.928103792134824e-05</v>
+        <v>0.08288948527494226</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,160 +6510,160 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.04364248204276616</v>
+        <v>-0.003556006410200875</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.0290997686509115</v>
+        <v>0.04696491142912747</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.003584413006599407</v>
+        <v>0.01979445435317176</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01457833939622871</v>
+        <v>-0.05825554232443009</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.003784619043013253</v>
+        <v>0.06758532018844049</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01309207742755787</v>
+        <v>0.009221683396484609</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.002790023986869106</v>
+        <v>-0.1323742820539895</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.03370323249114187</v>
+        <v>0.05118096660822694</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.01780035997224232</v>
+        <v>-0.1377094537286492</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01177295191943037</v>
+        <v>-0.02679888939136034</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03092198253517786</v>
+        <v>0.05370771020365889</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.02797184681190083</v>
+        <v>-0.1256822885743114</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.04321191412984603</v>
+        <v>0.1497332272402689</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02635984894689211</v>
+        <v>0.01923534238427907</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.001652416676666715</v>
+        <v>0.07346886067218884</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.0227866533017265</v>
+        <v>-0.1099888317545137</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.008752192900537036</v>
+        <v>-0.02408889970627489</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.05840082905191733</v>
+        <v>-0.06849378327006239</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.02542666110425614</v>
+        <v>0.08207124290076601</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2151232634366411</v>
+        <v>0.3588137352364056</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.125831006257515</v>
+        <v>-0.18368938320164</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01975825082310381</v>
+        <v>-0.03008651787190362</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6716,28 +6716,28 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1324686292305458</v>
+        <v>0.3680669564366756</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1238636323942821</v>
+        <v>-0.2051462521058612</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.04393479183065603</v>
+        <v>-0.08282142268178171</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,22 +6746,22 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05049415296528832</v>
+        <v>0.04579259625390512</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.01205387435702944</v>
+        <v>-0.02203885350107665</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03886643548731699</v>
+        <v>-0.05300866887313786</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
@@ -6770,46 +6770,46 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1126778764393452</v>
+        <v>-0.09542348559778471</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.01192689869407794</v>
+        <v>-0.09750986450180653</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02054553340266173</v>
+        <v>-0.07313543792606328</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.00424314970866375</v>
+        <v>0.1150468412192538</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.02767040638558486</v>
+        <v>-0.0934465518416667</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.06314866859785818</v>
+        <v>0.03930370773170528</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,25 +6818,25 @@
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3145494462794939</v>
+        <v>0.2854600222335695</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03819176471313902</v>
+        <v>-0.1078622213859597</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1265751348276277</v>
+        <v>-0.161020591713576</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6845,34 +6845,34 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.01595124719892993</v>
+        <v>-0.0004774772774915518</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.06433531018684535</v>
+        <v>-0.03237072580025979</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1000932622341642</v>
+        <v>-0.001832128906475454</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1149289919296314</v>
+        <v>-0.005020473088975051</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.00433160687371005</v>
+        <v>0.02469853001009788</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1121136701862579</v>
+        <v>0.07075002342157624</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1732724226069885</v>
+        <v>0.2243274540682243</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.03061608193782053</v>
+        <v>-0.1153847414602915</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07473837500575017</v>
+        <v>-0.05688797849886992</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.04611260422243151</v>
+        <v>-0.1173366669197679</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.002814616725125711</v>
+        <v>0.110887652822712</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01393687515273088</v>
+        <v>0.01235661457565912</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.06228172463049267</v>
+        <v>-0.06304728378537303</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.1157866838764998</v>
+        <v>0.2254816416729415</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06224465909588221</v>
+        <v>0.02656287427409669</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,16 +6989,16 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.01714648253768487</v>
+        <v>-0.1078495374151546</v>
       </c>
       <c r="CX12" t="n">
         <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.01187790992153187</v>
+        <v>0.1218008414819913</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.008997525834546735</v>
+        <v>0.01779849746782414</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,22 +7016,22 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.0498810104100236</v>
+        <v>-0.08553886893477874</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01203091131986449</v>
+        <v>0.01523079663111239</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06880796818952743</v>
+        <v>-0.07326298025770951</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,43 +7043,43 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.05658511468752801</v>
+        <v>-0.0761430205984933</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01088576205655713</v>
+        <v>0.0696780864127871</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.03821078303779638</v>
+        <v>0.004717508669616704</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.04337956069217432</v>
+        <v>0.0399493145285781</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.03788258053997143</v>
+        <v>-0.03478956897366541</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.01353619314625233</v>
+        <v>0.01517753512252048</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7088,61 +7088,61 @@
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0004455789260190874</v>
+        <v>-0.06564013940548112</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.03190212051016422</v>
+        <v>0.08448402046871774</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05300608510151972</v>
+        <v>0.03868860389256683</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03346797928680433</v>
+        <v>-0.04594131921122375</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01957711382439269</v>
+        <v>0.07446450136762654</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04259212102933813</v>
+        <v>-0.03992585139435588</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,22 +7151,22 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.02954159095461096</v>
+        <v>-0.1229205981467932</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.005565173325091996</v>
+        <v>0.1291131533909924</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.006081434250456462</v>
+        <v>-0.004393802163489989</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7175,19 +7175,19 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.05430330758712323</v>
+        <v>-0.07300158090547476</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01490508380489151</v>
+        <v>0.0674811004662326</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03358604049945919</v>
+        <v>-0.006457043170660081</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,28 +7196,28 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.05187517834887407</v>
+        <v>-0.02537155685195356</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.05036674832939306</v>
+        <v>0.1096516984463757</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.07038304999014991</v>
+        <v>-0.01565525753308386</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7226,34 +7226,34 @@
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.0023408523798144</v>
+        <v>-0.09571933358654419</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.0753584946647541</v>
+        <v>0.06758209673983731</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4449049544548089</v>
+        <v>0.3607336140234289</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1059310510329614</v>
+        <v>0.0473038980827926</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3463082650588206</v>
+        <v>-0.3246290536863282</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3284230744185743</v>
+        <v>0.5258093956468092</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.09566865540421467</v>
+        <v>0.0004484127817481917</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.345752346063022</v>
+        <v>-0.322847337944463</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06162918843150633</v>
+        <v>0.1285450710110913</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.004255765368220705</v>
+        <v>-0.1945802157187417</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.00298593295894474</v>
+        <v>-0.04483259724062288</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06562434265177598</v>
+        <v>-0.04390635670724047</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.05220029159030608</v>
+        <v>-0.3670506297640307</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.03295658186806767</v>
+        <v>-0.2498071599766583</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,22 +7369,22 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.06880628526096823</v>
+        <v>0.07841384935317826</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0001010337539613481</v>
+        <v>-0.03289130806533601</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.06638850902049946</v>
+        <v>-0.1616781356325394</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.3897971262794842</v>
+        <v>0.8150804606820405</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,67 +7405,67 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01830963239499248</v>
+        <v>-0.1462108403064315</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1606340238454899</v>
+        <v>-0.1586639852713649</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1072441122294851</v>
+        <v>-0.1389570847533828</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1031619291080369</v>
+        <v>-0.130173278183207</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.1162629852614356</v>
+        <v>-0.1830965822362538</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1382127062960247</v>
+        <v>0.1193339972790273</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.08159815715518606</v>
+        <v>0.1146678649872982</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.03012508059879611</v>
+        <v>-0.005398154042253047</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -7474,76 +7474,76 @@
         <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2028925183807914</v>
+        <v>0.4194036007887761</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.04831194544062689</v>
+        <v>-0.2156315239793941</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1055559779566081</v>
+        <v>-0.2613290824343849</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.08981095276235199</v>
+        <v>-0.1481411216570734</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.009741957777483856</v>
+        <v>0.05573820404603513</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.07984964463347302</v>
+        <v>0.1452947384042942</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.08817590468854479</v>
+        <v>-0.3961263320279579</v>
       </c>
       <c r="CO13" t="n">
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.04267297758471202</v>
+        <v>0.4304310101439402</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.008504614481452176</v>
+        <v>0.3364702923276489</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7558,103 +7558,103 @@
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.06617730232812877</v>
+        <v>-0.1359939628615277</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.006865325384676831</v>
+        <v>0.02156513678992223</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.08446731505763078</v>
+        <v>0.1108376753854639</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.07163702492287373</v>
+        <v>0.00942710255327054</v>
       </c>
       <c r="DG13" t="n">
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01629356248931477</v>
+        <v>-0.1233862250064237</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.01100343696205065</v>
+        <v>-0.01007122558320455</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.06067934966281456</v>
+        <v>0.02090521558865856</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.02193877786832778</v>
+        <v>0.03671965996002531</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.003160431760741389</v>
+        <v>0.07249801710184893</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.006861474389601172</v>
+        <v>0.1225386741444625</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.002092638976165289</v>
+        <v>-0.03420557684249884</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.02337246147823559</v>
+        <v>0.06652201866734407</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
@@ -7666,34 +7666,34 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03062935135742284</v>
+        <v>-0.05203797337908683</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01962783863751532</v>
+        <v>-0.04880972600610293</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0725957799712852</v>
+        <v>8.947008204225261e-05</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.009190272091584836</v>
+        <v>-0.003047820732449796</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,13 +7702,13 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01964834781810592</v>
+        <v>-0.02569526005479601</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07828470056017631</v>
+        <v>0.1294554279146467</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,55 +7717,55 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.05999074822635489</v>
+        <v>-0.1710503268062409</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.005742369963835867</v>
+        <v>0.006987703138168511</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0841886927577494</v>
+        <v>0.1256121979940393</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.05534608688514023</v>
+        <v>-0.1730705727749073</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.01211675354548226</v>
+        <v>0.06566941556617122</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.05393127177827076</v>
+        <v>-0.0784574620779309</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,19 +7774,19 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01046679449754562</v>
+        <v>0.06164362891934676</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.05260510035760908</v>
+        <v>0.08630312784449636</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01017861701834309</v>
+        <v>-0.02745105689399636</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,25 +7795,25 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.03558563725014079</v>
+        <v>-0.04485330505443272</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.03914781853227595</v>
+        <v>0.05698642866600107</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,43 +7830,43 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4682573534651062</v>
+        <v>0.2794183900095817</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.140243157273693</v>
+        <v>-0.1927902998245362</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1247710308321576</v>
+        <v>-0.01912798609395653</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2901084260252085</v>
+        <v>0.2918271550759456</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1133715656247606</v>
+        <v>-0.2225417831113984</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1103659745051044</v>
+        <v>-0.1227524644521557</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,73 +7881,73 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.09450879257038963</v>
+        <v>0.04177018005089975</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.01464582630023788</v>
+        <v>-0.038285938639717</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04376526981732214</v>
+        <v>-0.07508506618308279</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.09707238975251577</v>
+        <v>0.003532648773686602</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.001973680560298761</v>
+        <v>-0.2080808681701728</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.0009454918587321753</v>
+        <v>-0.1427008393296628</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.006300901886431578</v>
+        <v>0.1478445413940936</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.06908981192357057</v>
+        <v>-0.1176127278692825</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.08382604644178974</v>
+        <v>0.06528434407327294</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7962,79 +7962,79 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3962046179815384</v>
+        <v>0.3611764138421967</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0551477997507259</v>
+        <v>-0.03979895715384468</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.06665661117764873</v>
+        <v>-0.2945621457365663</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.01681749698111582</v>
+        <v>-0.0163772111714898</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.07522056503357362</v>
+        <v>-0.05390777046180553</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1707578816402287</v>
+        <v>0.08393641439579619</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1069373374890849</v>
+        <v>0.08817558440614211</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04696575043555137</v>
+        <v>0.02042971467739034</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1364410846440818</v>
+        <v>0.1232766113711953</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,46 +8043,46 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1904076867160967</v>
+        <v>0.2724773311564883</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.06140016290702721</v>
+        <v>-0.1348392625462305</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.02585074720846988</v>
+        <v>-0.07230557365666607</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1049694886354399</v>
+        <v>-0.08612240440607952</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.009035639993685906</v>
+        <v>0.1084237019761549</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01488724743259783</v>
+        <v>0.05208628691456477</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -8100,16 +8100,16 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.01022669608226754</v>
+        <v>-0.1771449398732975</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.09983269158227712</v>
+        <v>0.27078597529719</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.08579439714495488</v>
+        <v>0.0903804945895461</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
@@ -8118,28 +8118,28 @@
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.08350876504362814</v>
+        <v>-0.0668890165882851</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02848350057685259</v>
+        <v>0.1289119375835419</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01678564720254667</v>
+        <v>0.06271219768989943</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.003530164935685697</v>
+        <v>-0.0005075575826599685</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.01867025625253424</v>
+        <v>0.01122295991431843</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03520939960272301</v>
+        <v>-0.06882009243136906</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8181,43 +8181,43 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.03856106766063016</v>
+        <v>-0.1450319974749367</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.06347431082306511</v>
+        <v>-0.07905686378717934</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.05917758693003628</v>
+        <v>0.02687552607017286</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.03005289852790697</v>
+        <v>0.03601438620411392</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.002737622315463555</v>
+        <v>0.01606357496586452</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.07547928463470804</v>
+        <v>-0.1629042904248346</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8229,22 +8229,22 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.09092189173011028</v>
+        <v>0.03342830698566209</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.03342161635398625</v>
+        <v>0.06293869523676252</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.07689933698107632</v>
+        <v>0.07626978146811693</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.05927599522268782</v>
+        <v>-0.04239371963496291</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02237318903198982</v>
+        <v>0.08928271300733645</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02249283909840693</v>
+        <v>-0.08263116573963464</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,73 +8286,73 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.0849214988914625</v>
+        <v>-0.08469665660097823</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0180725538424764</v>
+        <v>0.1313216129837109</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.009768315807713876</v>
+        <v>0.03737022483431131</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.0001026157985287217</v>
+        <v>0.004629263475003626</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.06539476519358232</v>
+        <v>0.0496191547818408</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.08139893030841194</v>
+        <v>-0.04615262759837505</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.007812997463262953</v>
+        <v>-0.01000564844837484</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.01914586120555678</v>
+        <v>0.07220355614126961</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.01170226628051469</v>
+        <v>-0.04788716694502342</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8364,28 +8364,28 @@
         <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.005553042034291465</v>
+        <v>-0.05866738737383986</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.06496630861189694</v>
+        <v>0.06596541503258582</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
         <v>-0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>0</v>
@@ -8399,16 +8399,16 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>1.112268887086421</v>
+        <v>0.5408382746374865</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4649456889397904</v>
+        <v>-0.4815925950480091</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.485831606248343</v>
+        <v>0.1148784678054574</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8426,16 +8426,16 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8651561789667916</v>
+        <v>0.4995809188349294</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3952992823390921</v>
+        <v>-0.5511451305462036</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.460525965282252</v>
+        <v>-0.009687368328769605</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -8444,34 +8444,34 @@
         <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2296941632517095</v>
+        <v>0.1722443984458736</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.06784313495108012</v>
+        <v>-0.1387282276814258</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.02314778804164243</v>
+        <v>-0.1384269443903506</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -8480,22 +8480,22 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2412114390956148</v>
+        <v>-0.1409602841764058</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.1009274102452145</v>
+        <v>-0.2835313227593712</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.08944714909840515</v>
+        <v>-0.1053993879460941</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8504,25 +8504,25 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.1999330214104973</v>
+        <v>0.169551236525831</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.01431811081225817</v>
+        <v>-0.1779731082082996</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.09221159567540738</v>
+        <v>0.1248583505452361</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8534,19 +8534,19 @@
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.9060126124911332</v>
+        <v>0.5710485552068003</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.0872635573915892</v>
+        <v>-0.3395437651661568</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.04215708527972121</v>
+        <v>-0.2781118880104803</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>-0</v>
@@ -8558,19 +8558,19 @@
         <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.08556172596747143</v>
+        <v>-0.05285389621454308</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.2001041936257979</v>
+        <v>-0.1191067339677571</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.4004198490046216</v>
+        <v>0.03499584149133572</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -8588,16 +8588,16 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1254046968654189</v>
+        <v>0.05088210585760489</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.05766376285856157</v>
+        <v>0.04648378918701392</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.08905162644068269</v>
+        <v>0.07634642298148507</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
@@ -8615,19 +8615,19 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.5752264551642292</v>
+        <v>0.43441942759135</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.1148565304731582</v>
+        <v>-0.2386169607203666</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.01291490459535738</v>
+        <v>-0.08366976352504017</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8642,16 +8642,16 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1989558603333093</v>
+        <v>-0.115374327493779</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.09557040622581658</v>
+        <v>0.2220249193713621</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.03780890078107411</v>
+        <v>0.003864352511796912</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
@@ -8663,25 +8663,25 @@
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.06140052328873045</v>
+        <v>-0.1643318139218358</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.003501263801217726</v>
+        <v>0.4242484087702279</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.2061367988431194</v>
+        <v>0.2875267236346035</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8693,19 +8693,19 @@
         <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.1613048248733637</v>
+        <v>-0.1058215826683313</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.1188222537081343</v>
+        <v>0.2382073531875977</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.02580430642807263</v>
+        <v>0.02685080445611974</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8723,43 +8723,43 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.04760409369680486</v>
+        <v>-0.05487086238354853</v>
       </c>
       <c r="DG15" t="n">
         <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0836786614842452</v>
+        <v>0.01542084995791159</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.003194786825850377</v>
+        <v>0.001665603469129668</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.04603866819897</v>
+        <v>-0.1176337432035223</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.00469781917878522</v>
+        <v>0.03135220501957383</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.1015199506877748</v>
+        <v>0.02752959525685761</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8768,31 +8768,31 @@
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0616969093678851</v>
+        <v>-0.04138933865184768</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.1218931935705604</v>
+        <v>-0.07179443407336143</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.04993469857318637</v>
+        <v>-0.0453787839193129</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
         <v>0</v>
@@ -8804,16 +8804,16 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.1436826429147691</v>
+        <v>-0.1535655319223179</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.1047312590987905</v>
+        <v>0.1957942352995074</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1339289155766028</v>
+        <v>0.04769421346287007</v>
       </c>
       <c r="EK15" t="n">
         <v>-0</v>
@@ -8831,22 +8831,22 @@
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.0962776304943405</v>
+        <v>-0.09052893936884121</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.08810007755722381</v>
+        <v>0.1806165880217258</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.08831035700405176</v>
+        <v>-0.01120257625065933</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8858,106 +8858,106 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1660134294499603</v>
+        <v>-0.1605146898478675</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.1477948573029332</v>
+        <v>0.249714027848105</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01605922030537523</v>
+        <v>0.008865348619931865</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.1020251612372549</v>
+        <v>-0.07067997045532269</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.09154078336923696</v>
+        <v>0.1551689715994177</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.04723679605306765</v>
+        <v>-0.05288076647531971</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.02277779299447229</v>
+        <v>-0.0307737591270067</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.3385392337980968</v>
+        <v>-0.2192915943838195</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.01784399197774636</v>
+        <v>-0.02651101082962393</v>
       </c>
       <c r="FU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
         <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.02235079110482602</v>
+        <v>-0.1252920615696027</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.003026383278160862</v>
+        <v>0.1206821535233279</v>
       </c>
       <c r="GC15" t="n">
         <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
         <v>-0</v>
